--- a/data/trans_dic/Q25_A_R3-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/Q25_A_R3-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de fumar hace menos tiempo (3.374 años)</t>
+          <t>Población que dejo de fumar hace menos tiempo (3.374 años) (tasa de respuesta: 96,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,78; 19,98</t>
+          <t>11,66; 19,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,84; 19,99</t>
+          <t>12,56; 20,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,26; 20,79</t>
+          <t>11,47; 20,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,84; 17,78</t>
+          <t>8,0; 17,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,93; 40,41</t>
+          <t>15,84; 40,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,37; 51,38</t>
+          <t>28,65; 52,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,1; 34,87</t>
+          <t>9,23; 36,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,16; 39,7</t>
+          <t>11,19; 38,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,32; 21,4</t>
+          <t>13,2; 21,32</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,55; 23,77</t>
+          <t>16,21; 23,85</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,28; 20,93</t>
+          <t>12,44; 20,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,12; 19,43</t>
+          <t>10,46; 19,41</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,09; 38,67</t>
+          <t>25,69; 37,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,1; 42,63</t>
+          <t>31,88; 42,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,18; 33,92</t>
+          <t>24,0; 34,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,17; 85,24</t>
+          <t>14,3; 82,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,42; 51,73</t>
+          <t>36,09; 50,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,01; 42,34</t>
+          <t>30,04; 42,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,43; 42,68</t>
+          <t>28,32; 41,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,34; 35,45</t>
+          <t>23,84; 35,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,31; 40,8</t>
+          <t>30,96; 41,31</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32,42; 40,78</t>
+          <t>32,4; 40,87</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27,28; 35,33</t>
+          <t>27,54; 35,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,04; 77,56</t>
+          <t>20,05; 77,64</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,73; 42,04</t>
+          <t>21,33; 42,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,39; 43,85</t>
+          <t>22,98; 44,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,38; 33,03</t>
+          <t>14,88; 33,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,28; 26,73</t>
+          <t>11,79; 26,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,22; 46,61</t>
+          <t>19,86; 47,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,47; 46,13</t>
+          <t>24,83; 46,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,34; 35,89</t>
+          <t>18,87; 36,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,58; 30,94</t>
+          <t>15,03; 31,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24,51; 40,85</t>
+          <t>24,05; 40,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,29; 41,05</t>
+          <t>26,53; 41,5</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19,6; 31,94</t>
+          <t>19,73; 31,7</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,41; 25,62</t>
+          <t>15,43; 26,29</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,43; 27,33</t>
+          <t>20,28; 27,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,74; 30,34</t>
+          <t>23,65; 30,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,11; 26,97</t>
+          <t>20,09; 26,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,34; 70,43</t>
+          <t>14,13; 74,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,55; 43,81</t>
+          <t>31,47; 43,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,08; 41,17</t>
+          <t>31,07; 41,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,65; 36,31</t>
+          <t>26,66; 35,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,52; 31,21</t>
+          <t>22,42; 30,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,84; 30,81</t>
+          <t>24,6; 30,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27,37; 32,66</t>
+          <t>27,33; 32,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23,58; 28,9</t>
+          <t>23,69; 28,89</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,4; 66,05</t>
+          <t>18,52; 65,11</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de fumar hace menos tiempo (3.374 años)</t>
+          <t>Población que dejo de fumar hace menos tiempo (3.374 años) (tasa de respuesta: 96,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>34941; 59269</t>
+          <t>34598; 58968</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>49367; 76844</t>
+          <t>48264; 78113</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26652; 49182</t>
+          <t>27137; 48590</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12653; 28706</t>
+          <t>12909; 28480</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8055; 20430</t>
+          <t>8010; 20237</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19878; 36004</t>
+          <t>20077; 36698</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4707; 16247</t>
+          <t>4302; 17176</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4724; 16800</t>
+          <t>4735; 16295</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>46261; 74308</t>
+          <t>45823; 74037</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>75199; 108043</t>
+          <t>73682; 108377</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34770; 59288</t>
+          <t>35225; 59076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20620; 39585</t>
+          <t>21306; 39544</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>60889; 90232</t>
+          <t>59955; 87414</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>111775; 148466</t>
+          <t>111027; 147956</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85499; 119931</t>
+          <t>84873; 121625</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>76763; 461684</t>
+          <t>77452; 447513</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52433; 76570</t>
+          <t>53416; 75299</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>72977; 102959</t>
+          <t>73036; 102184</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>67576; 98012</t>
+          <t>65024; 96343</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48728; 70992</t>
+          <t>47744; 71418</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>119399; 155594</t>
+          <t>118086; 157523</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>191721; 241182</t>
+          <t>191639; 241732</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>159087; 206048</t>
+          <t>160590; 206737</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>148649; 575382</t>
+          <t>148742; 576014</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17205; 34881</t>
+          <t>17697; 35011</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21322; 41754</t>
+          <t>21884; 41939</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16601; 33472</t>
+          <t>15079; 33851</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16811; 36594</t>
+          <t>16141; 36724</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10087; 23254</t>
+          <t>9908; 23591</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19058; 35932</t>
+          <t>19337; 36362</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19145; 37459</t>
+          <t>19693; 38125</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13474; 26748</t>
+          <t>12991; 26892</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>32572; 54283</t>
+          <t>31952; 53985</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45511; 71064</t>
+          <t>45922; 71842</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40313; 65695</t>
+          <t>40591; 65221</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>34409; 57232</t>
+          <t>34473; 58715</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>125205; 167489</t>
+          <t>124287; 166633</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>196522; 251189</t>
+          <t>195806; 249507</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>139048; 186498</t>
+          <t>138957; 186544</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>120474; 591547</t>
+          <t>118685; 628904</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>78394; 108845</t>
+          <t>78185; 108434</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>121547; 161016</t>
+          <t>121524; 162416</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>101439; 138175</t>
+          <t>101460; 136942</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>74079; 102687</t>
+          <t>73779; 100454</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>213945; 265436</t>
+          <t>211891; 265948</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>333682; 398064</t>
+          <t>333130; 396541</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>252786; 309876</t>
+          <t>253989; 309708</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>215113; 772086</t>
+          <t>216470; 761106</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Q25_A_R3-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/Q25_A_R3-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,66; 19,88</t>
+          <t>11,33; 20,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,56; 20,32</t>
+          <t>13,02; 20,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,47; 20,54</t>
+          <t>11,61; 20,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,0; 17,64</t>
+          <t>8,11; 18,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,84; 40,03</t>
+          <t>15,6; 40,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,65; 52,37</t>
+          <t>28,08; 53,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,23; 36,86</t>
+          <t>9,29; 34,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,19; 38,51</t>
+          <t>10,43; 33,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,2; 21,32</t>
+          <t>13,21; 21,34</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,21; 23,85</t>
+          <t>16,2; 23,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,44; 20,86</t>
+          <t>12,64; 21,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,46; 19,41</t>
+          <t>9,84; 19,45</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>21,86%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,69; 37,46</t>
+          <t>26,26; 37,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,88; 42,49</t>
+          <t>32,13; 42,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,0; 34,4</t>
+          <t>23,67; 33,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,3; 82,62</t>
+          <t>11,95; 20,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,09; 50,87</t>
+          <t>35,7; 51,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,04; 42,02</t>
+          <t>29,34; 41,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,32; 41,96</t>
+          <t>29,08; 42,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,84; 35,67</t>
+          <t>25,37; 36,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,96; 41,31</t>
+          <t>31,63; 41,32</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32,4; 40,87</t>
+          <t>32,25; 40,5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27,54; 35,45</t>
+          <t>27,1; 35,3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,05; 77,64</t>
+          <t>18,63; 25,76</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,5%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,33; 42,19</t>
+          <t>22,09; 43,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,98; 44,04</t>
+          <t>23,35; 44,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,88; 33,4</t>
+          <t>15,65; 33,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,79; 26,83</t>
+          <t>12,38; 26,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,86; 47,28</t>
+          <t>20,26; 47,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,83; 46,69</t>
+          <t>24,53; 46,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,87; 36,53</t>
+          <t>19,02; 35,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,03; 31,1</t>
+          <t>14,38; 30,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24,05; 40,63</t>
+          <t>24,37; 40,72</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,53; 41,5</t>
+          <t>26,3; 41,47</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19,73; 31,7</t>
+          <t>18,77; 32,36</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,43; 26,29</t>
+          <t>14,14; 25,32</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>19,59%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,28; 27,19</t>
+          <t>20,69; 27,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,65; 30,14</t>
+          <t>23,85; 30,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,09; 26,97</t>
+          <t>20,31; 26,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,13; 74,87</t>
+          <t>12,59; 18,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,47; 43,64</t>
+          <t>31,96; 44,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,07; 41,53</t>
+          <t>31,47; 41,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,66; 35,98</t>
+          <t>26,24; 36,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,42; 30,53</t>
+          <t>23,0; 30,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,6; 30,87</t>
+          <t>24,84; 30,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27,33; 32,53</t>
+          <t>27,45; 33,11</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23,69; 28,89</t>
+          <t>23,6; 29,1</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,52; 65,11</t>
+          <t>17,11; 22,21</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19642</t>
+          <t>21249</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8720</t>
+          <t>8939</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28362</t>
+          <t>30187</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>34598; 58968</t>
+          <t>33612; 59768</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>48264; 78113</t>
+          <t>50063; 77778</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27137; 48590</t>
+          <t>27480; 48842</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12909; 28480</t>
+          <t>13931; 31276</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8010; 20237</t>
+          <t>7889; 20334</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20077; 36698</t>
+          <t>19674; 37265</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4302; 17176</t>
+          <t>4329; 15849</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4735; 16295</t>
+          <t>4674; 15066</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45823; 74037</t>
+          <t>45870; 74085</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>73682; 108377</t>
+          <t>73638; 107482</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35225; 59076</t>
+          <t>35801; 60325</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21306; 39544</t>
+          <t>21318; 42112</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>291142</t>
+          <t>52632</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>59142</t>
+          <t>67337</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>350284</t>
+          <t>119969</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>59955; 87414</t>
+          <t>61276; 88591</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>111027; 147956</t>
+          <t>111888; 146934</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>84873; 121625</t>
+          <t>83700; 118313</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>77452; 447513</t>
+          <t>39415; 66817</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>53416; 75299</t>
+          <t>52848; 76477</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>73036; 102184</t>
+          <t>71343; 102051</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65024; 96343</t>
+          <t>66765; 97109</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>47744; 71418</t>
+          <t>55590; 80596</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>118086; 157523</t>
+          <t>120606; 157578</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>191639; 241732</t>
+          <t>190716; 239532</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>160590; 206737</t>
+          <t>158054; 205882</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>148742; 576014</t>
+          <t>102252; 141378</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25330</t>
+          <t>27532</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19537</t>
+          <t>19943</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>44867</t>
+          <t>47474</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17697; 35011</t>
+          <t>18334; 36092</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21884; 41939</t>
+          <t>22239; 42601</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15079; 33851</t>
+          <t>15860; 33441</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16141; 36724</t>
+          <t>18408; 39778</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9908; 23591</t>
+          <t>10111; 23449</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19337; 36362</t>
+          <t>19106; 36286</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19693; 38125</t>
+          <t>19845; 37430</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12991; 26892</t>
+          <t>13643; 28548</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>31952; 53985</t>
+          <t>32376; 54100</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45922; 71842</t>
+          <t>45529; 71788</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40591; 65221</t>
+          <t>38618; 66560</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>34473; 58715</t>
+          <t>34436; 61642</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>336115</t>
+          <t>101413</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>87399</t>
+          <t>96218</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>423513</t>
+          <t>197631</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>124287; 166633</t>
+          <t>126793; 168183</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>195806; 249507</t>
+          <t>197477; 249396</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>138957; 186544</t>
+          <t>140477; 186040</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>118685; 628904</t>
+          <t>81834; 120168</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>78185; 108434</t>
+          <t>79418; 109802</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>121524; 162416</t>
+          <t>123096; 161109</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>101460; 136942</t>
+          <t>99856; 137133</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>73779; 100454</t>
+          <t>82521; 111045</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>211891; 265948</t>
+          <t>213966; 266848</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>333130; 396541</t>
+          <t>334545; 403641</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>253989; 309708</t>
+          <t>252977; 312026</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>216470; 761106</t>
+          <t>172628; 224037</t>
         </is>
       </c>
     </row>
